--- a/site/exports/bnu-economics-business-administration.xlsx
+++ b/site/exports/bnu-economics-business-administration.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>经济与工商管理学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>现职unknown；目录、历史角色与开放任期不等于观察日人事确认。；仅必要官网职业摘录与书目；未独立核出版元数据或全文。；法律授位实体未独立核验；学习时间与授位时间分开。；目录原始href、页面文本链接导航和浏览器页面导航分别记载，不互相替代。；3项学位由官方PDF明确获得及年份支持；学习结束月份不补为授位月份。；博士后与访问学者属非学位分类，不当作官网明确否认授位。；4条阶段或访问合作关系不升级正式论文导师；本人导师资格不当作自己的导师。；目录数字经济与管理系与个人页市场营销系分源保留，变更原因和先后unknown。；主编与论文作者分开，主编作品完整作者表unknown。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：创业管理；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科、MBA；来源ID：new-recovery-bnu-zhaoxiangyang-s001-a7ff1a7fb0a4；https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html | 跨文化管理；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科、MBA；来源ID：new-recovery-bnu-zhaoxiangyang-s001-a7ff1a7fb0a4；https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html | 跨文化沟通；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：全校公选课；来源ID：new-recovery-bnu-zhaoxiangyang-s001-a7ff1a7fb0a4；https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html | 国际管理（或全球商务）；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科；来源ID：new-recovery-bnu-zhaoxiangyang-s001-a7ff1a7fb0a4；https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html | 管理案例分析；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：MBA；来源ID：new-recovery-bnu-zhaoxiangyang-s001-a7ff1a7fb0a4；https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -957,13 +1011,407 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>物理学学士</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>陕西师范大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1989-09</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1993-07</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>理论物理</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>官网履历给学习年月及学位标签，官方MBA介绍另明确先后获得三学位并给年份；获授年采用后者，未把学习结束月份当授位月。博士研究方向不自动视作授予学位专业。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_label_as_source：学士；来源education_stage：本科；来源department：物理系；来源date_as_source：1989/9---1993/7；来源学位标签：学士</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://bs.bnu.edu.cn/docs/2019-01/20190102112621421399.pdf</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>心理学硕士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1998-09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2001-07</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>官网履历给学习年月及学位标签，官方MBA介绍另明确先后获得三学位并给年份；获授年采用后者，未把学习结束月份当授位月。博士研究方向不自动视作授予学位专业。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_label_as_source：硕士；来源education_stage：硕士；来源department：心理系；来源date_as_source：1998/9---2001/7；来源学位标签：硕士</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://bs.bnu.edu.cn/docs/2019-01/20190102112621421399.pdf</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>德国吉森（Giessen）大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2002-08</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2005-06</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>官网履历给学习年月及学位标签，官方MBA介绍另明确先后获得三学位并给年份；获授年采用后者，未把学习结束月份当授位月。博士研究方向不自动视作授予学位专业。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：心理系；来源date_as_source：2002/8---2005/6；来源记载（award_institution_as_source）：德国吉森大学</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://bs.bnu.edu.cn/docs/2019-01/20190102112621421399.pdf</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_training</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>浙江大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2005-12</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2006-10</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>明确非授位事件；合作导师仅限所列博士后/访问阶段。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：管理学院；来源记载（event_kind）：postdoctoral_training</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>加拿大Simon Fraser University</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2005-07</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2005-11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>明确非授位事件；合作导师仅限所列博士后/访问阶段。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：商学院</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>历任讲师、副教授</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2006-11</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>未分别给讲师、副教授起止时间，不推晋升日期；迄今不作观察日实时人事认证。；任职按留存来源表述保留；不据此认证当前人事状态。；来源date_as_source：2006/11-迄今；来源记载（院系）：经济与工商管理学院</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -975,14 +1423,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26.6" customWidth="1" min="2" max="2"/>
+    <col width="46.2" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="61.59999999999999" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="22.4" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -1108,10 +1556,214 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>朱滢</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网明确阶段指导关系；没有论文指导语境或原论文核验，不提升为正式论文导师，不依合著反推。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Prof. Michael Frese</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网明确阶段指导关系；没有论文指导语境或原论文核验，不提升为正式论文导师，不依合著反推。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>王重鸣</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_collaborating_mentor</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网明确阶段指导关系；没有论文指导语境或原论文核验，不提升为正式论文导师，不依合著反推。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Prof. Rosalie Tung</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>visiting_collaborating_mentor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网明确阶段指导关系；没有论文指导语境或原论文核验，不提升为正式论文导师，不依合著反推。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1123,19 +1775,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26.6" customWidth="1" min="2" max="2"/>
+    <col width="36.4" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="44.8" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="64.39999999999999" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1314,8 +1966,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>创业活动的国家差异：文化与国家经济发展水平的交互作用</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：赵向阳、李海、Andreas Rauch</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>北师大MBA管理案例精选（第一辑）</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>edited_book_as_official_list</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源editors_as_source：赵向阳、孙舒平；来源person_contribution_role_as_source：主编；来源书目信息（date_as_source）：2015/10；来源书目信息（author_list_status）：editor_list_not_author_list</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1323,6 +2079,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1334,14 +2094,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40.59999999999999" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1494,12 +2254,126 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-zhaoxiangyang-s001-a7ff1a7fb0a4</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://bshr.bnu.edu.cn/Public/htm/news/5/1030.html</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T03:42:11.329Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-zhaoxiangyang-s002-f7489719a184</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://bs.bnu.edu.cn/szdw1/zrjs1/index.html</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T03:41:52.766Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>赵向阳</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-zhaoxiangyang-s003-0b0fda85316a</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://bs.bnu.edu.cn/docs/2019-01/20190102112621421399.pdf</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T03:42:28.983Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/bnu-economics-business-administration.xlsx
+++ b/site/exports/bnu-economics-business-administration.xlsx
@@ -1119,7 +1119,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="2" t="b">
@@ -1249,7 +1249,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="2" t="b">
